--- a/snu-narae.players.xlsx
+++ b/snu-narae.players.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/highmac/SnuBaseballTracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B906C09-1B55-0B48-841E-CFDD2CBACE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271F2DF1-F235-4442-BBBB-0954330120B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25600" yWindow="7860" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -942,9 +942,6 @@
     <t>wocjf8022@snu.ac.kr</t>
   </si>
   <si>
-    <t>김강민</t>
-  </si>
-  <si>
     <t>kangmin0716@snu.ac.kr</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -954,10 +951,6 @@
   </si>
   <si>
     <t>재약수</t>
-  </si>
-  <si>
-    <t>김강민</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>marskm0603@snu.ac.kr</t>
@@ -1627,6 +1620,12 @@
   </si>
   <si>
     <t>teamName</t>
+  </si>
+  <si>
+    <t>김강민2</t>
+  </si>
+  <si>
+    <t>김강민1</t>
   </si>
 </sst>
 </file>
@@ -2092,7 +2091,7 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2591,22 +2590,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4545,810 +4544,810 @@
     </row>
     <row r="99" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>277</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>278</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E99" s="7">
         <v>19</v>
       </c>
       <c r="F99" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="35" t="s">
-        <v>281</v>
+        <v>455</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E100" s="7">
         <v>29</v>
       </c>
       <c r="F100" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="35" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E101" s="7">
         <v>59</v>
       </c>
       <c r="F101" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="35" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E102" s="7">
         <v>77</v>
       </c>
       <c r="F102" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="35" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E103" s="7">
         <v>44</v>
       </c>
       <c r="F103" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="35" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E104" s="7">
         <v>98</v>
       </c>
       <c r="F104" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E105" s="7">
         <v>41</v>
       </c>
       <c r="F105" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="35" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E106" s="7">
         <v>24</v>
       </c>
       <c r="F106" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="35" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E107" s="7">
         <v>57</v>
       </c>
       <c r="F107" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="35" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E108" s="7">
         <v>22</v>
       </c>
       <c r="F108" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="35" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E109" s="7">
         <v>29</v>
       </c>
       <c r="F109" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="D110" s="6" t="s">
         <v>303</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>305</v>
       </c>
       <c r="E110" s="7">
         <v>56</v>
       </c>
       <c r="F110" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D111" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="B111" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="E111" s="7">
         <v>9</v>
       </c>
       <c r="F111" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D112" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="B112" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>311</v>
       </c>
       <c r="E112" s="7">
         <v>24</v>
       </c>
       <c r="F112" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="35" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E113" s="7">
         <v>64</v>
       </c>
       <c r="F113" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="35" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E114" s="7">
         <v>52</v>
       </c>
       <c r="F114" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="35" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E115" s="7">
         <v>5</v>
       </c>
       <c r="F115" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="35" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E116" s="7">
         <v>61</v>
       </c>
       <c r="F116" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="35" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E117" s="7">
         <v>0</v>
       </c>
       <c r="F117" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="35" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E118" s="7">
         <v>71</v>
       </c>
       <c r="F118" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="35" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E119" s="7">
         <v>60</v>
       </c>
       <c r="F119" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="35" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E120" s="7">
         <v>80</v>
       </c>
       <c r="F120" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="35" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E121" s="7">
         <v>53</v>
       </c>
       <c r="F121" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="35" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E122" s="7">
         <v>91</v>
       </c>
       <c r="F122" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="35" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E123" s="7">
         <v>38</v>
       </c>
       <c r="F123" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="35" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E124" s="7">
         <v>84</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="35" t="s">
+        <v>334</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C125" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="D125" s="6" t="s">
         <v>337</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>339</v>
       </c>
       <c r="E125" s="7">
         <v>29</v>
       </c>
       <c r="F125" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D126" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>342</v>
       </c>
       <c r="E126" s="7">
         <v>76</v>
       </c>
       <c r="F126" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="35" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E127" s="7">
         <v>74</v>
       </c>
       <c r="F127" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="35" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E128" s="7">
         <v>41</v>
       </c>
       <c r="F128" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="35" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E129" s="7">
         <v>34</v>
       </c>
       <c r="F129" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="35" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E130" s="7">
         <v>26</v>
       </c>
       <c r="F130" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="35" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E131" s="7">
         <v>51</v>
       </c>
       <c r="F131" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="35" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E132" s="7">
         <v>48</v>
       </c>
       <c r="F132" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="35" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E133" s="7">
         <v>31</v>
       </c>
       <c r="F133" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="35" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E134" s="7">
         <v>50</v>
       </c>
       <c r="F134" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="35" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E135" s="7">
         <v>21</v>
       </c>
       <c r="F135" s="32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="39" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C136" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D136" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E136" s="23">
         <v>28</v>
       </c>
       <c r="F136" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="35" t="s">
+        <v>363</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C137" s="24" t="s">
         <v>365</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="D137" s="24" t="s">
         <v>366</v>
-      </c>
-      <c r="C137" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="D137" s="24" t="s">
-        <v>368</v>
       </c>
       <c r="E137" s="7">
         <v>77</v>
       </c>
       <c r="F137" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="35" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C138" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D138" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E138" s="7">
         <v>53</v>
       </c>
       <c r="F138" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="35" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C139" s="22" t="s">
         <v>0</v>
@@ -5360,15 +5359,15 @@
         <v>47</v>
       </c>
       <c r="F139" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="35" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C140" s="22" t="s">
         <v>0</v>
@@ -5380,35 +5379,35 @@
         <v>38</v>
       </c>
       <c r="F140" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="35" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C141" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D141" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E141" s="7">
         <v>66</v>
       </c>
       <c r="F141" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="35" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C142" s="24" t="s">
         <v>82</v>
@@ -5420,15 +5419,15 @@
         <v>63</v>
       </c>
       <c r="F142" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="35" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C143" s="22" t="s">
         <v>0</v>
@@ -5440,27 +5439,27 @@
         <v>42</v>
       </c>
       <c r="F143" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="35" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C144" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D144" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E144" s="7">
         <v>25</v>
       </c>
       <c r="F144" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5468,7 +5467,7 @@
         <v>4</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C145" s="22" t="s">
         <v>0</v>
@@ -5480,35 +5479,35 @@
         <v>30</v>
       </c>
       <c r="F145" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="35" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C146" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D146" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E146" s="7">
         <v>95</v>
       </c>
       <c r="F146" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="35" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C147" s="22" t="s">
         <v>0</v>
@@ -5520,427 +5519,427 @@
         <v>3</v>
       </c>
       <c r="F147" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="35" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C148" s="22" t="s">
         <v>0</v>
       </c>
       <c r="D148" s="22" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E148" s="7">
         <v>8</v>
       </c>
       <c r="F148" s="32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="40" t="s">
+        <v>388</v>
+      </c>
+      <c r="B149" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="C149" s="26" t="s">
         <v>390</v>
       </c>
-      <c r="B149" s="25" t="s">
+      <c r="D149" s="26" t="s">
         <v>391</v>
-      </c>
-      <c r="C149" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="D149" s="26" t="s">
-        <v>393</v>
       </c>
       <c r="E149" s="27">
         <v>2</v>
       </c>
       <c r="F149" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="41" t="s">
+        <v>393</v>
+      </c>
+      <c r="B150" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="C150" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="B150" s="25" t="s">
+      <c r="D150" s="28" t="s">
         <v>396</v>
-      </c>
-      <c r="C150" s="28" t="s">
-        <v>397</v>
-      </c>
-      <c r="D150" s="28" t="s">
-        <v>398</v>
       </c>
       <c r="E150" s="29">
         <v>31</v>
       </c>
       <c r="F150" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="41" t="s">
+        <v>397</v>
+      </c>
+      <c r="B151" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="C151" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="B151" s="25" t="s">
+      <c r="D151" s="28" t="s">
         <v>400</v>
-      </c>
-      <c r="C151" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="D151" s="28" t="s">
-        <v>402</v>
       </c>
       <c r="E151" s="29">
         <v>21</v>
       </c>
       <c r="F151" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="40" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C152" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D152" s="26" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E152" s="27">
         <v>19</v>
       </c>
       <c r="F152" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="41" t="s">
+        <v>403</v>
+      </c>
+      <c r="B153" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="C153" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="D153" s="28" t="s">
         <v>405</v>
-      </c>
-      <c r="B153" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="C153" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="D153" s="28" t="s">
-        <v>407</v>
       </c>
       <c r="E153" s="29">
         <v>27</v>
       </c>
       <c r="F153" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="40" t="s">
+        <v>406</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="D154" s="26" t="s">
         <v>408</v>
-      </c>
-      <c r="B154" s="25" t="s">
-        <v>409</v>
-      </c>
-      <c r="C154" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="D154" s="26" t="s">
-        <v>410</v>
       </c>
       <c r="E154" s="27">
         <v>0</v>
       </c>
       <c r="F154" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="40" t="s">
+        <v>409</v>
+      </c>
+      <c r="B155" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="C155" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="D155" s="26" t="s">
         <v>411</v>
-      </c>
-      <c r="B155" s="25" t="s">
-        <v>412</v>
-      </c>
-      <c r="C155" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="D155" s="26" t="s">
-        <v>413</v>
       </c>
       <c r="E155" s="27">
         <v>10</v>
       </c>
       <c r="F155" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="41" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C156" s="28" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D156" s="28" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E156" s="29">
         <v>4</v>
       </c>
       <c r="F156" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="40" t="s">
+        <v>414</v>
+      </c>
+      <c r="B157" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="C157" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="D157" s="26" t="s">
         <v>416</v>
-      </c>
-      <c r="B157" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="C157" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="D157" s="26" t="s">
-        <v>418</v>
       </c>
       <c r="E157" s="27">
         <v>28</v>
       </c>
       <c r="F157" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="41" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C158" s="28" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D158" s="28" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E158" s="29">
         <v>80</v>
       </c>
       <c r="F158" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="41" t="s">
+        <v>419</v>
+      </c>
+      <c r="B159" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="C159" s="28" t="s">
         <v>421</v>
       </c>
-      <c r="B159" s="25" t="s">
+      <c r="D159" s="28" t="s">
         <v>422</v>
-      </c>
-      <c r="C159" s="28" t="s">
-        <v>423</v>
-      </c>
-      <c r="D159" s="28" t="s">
-        <v>424</v>
       </c>
       <c r="E159" s="29">
         <v>1</v>
       </c>
       <c r="F159" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="B160" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="C160" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="D160" s="26" t="s">
         <v>425</v>
-      </c>
-      <c r="B160" s="25" t="s">
-        <v>426</v>
-      </c>
-      <c r="C160" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="D160" s="26" t="s">
-        <v>427</v>
       </c>
       <c r="E160" s="27">
         <v>23</v>
       </c>
       <c r="F160" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="40" t="s">
+        <v>426</v>
+      </c>
+      <c r="B161" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="C161" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="D161" s="26" t="s">
         <v>428</v>
-      </c>
-      <c r="B161" s="25" t="s">
-        <v>429</v>
-      </c>
-      <c r="C161" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="D161" s="26" t="s">
-        <v>430</v>
       </c>
       <c r="E161" s="27">
         <v>74</v>
       </c>
       <c r="F161" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="40" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C162" s="26" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D162" s="26" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E162" s="27">
         <v>9</v>
       </c>
       <c r="F162" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="40" t="s">
+        <v>431</v>
+      </c>
+      <c r="B163" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="C163" s="26" t="s">
         <v>433</v>
       </c>
-      <c r="B163" s="25" t="s">
+      <c r="D163" s="26" t="s">
         <v>434</v>
-      </c>
-      <c r="C163" s="26" t="s">
-        <v>435</v>
-      </c>
-      <c r="D163" s="26" t="s">
-        <v>436</v>
       </c>
       <c r="E163" s="27">
         <v>36</v>
       </c>
       <c r="F163" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="40" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C164" s="26" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D164" s="26" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E164" s="27">
         <v>12</v>
       </c>
       <c r="F164" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="40" t="s">
+        <v>437</v>
+      </c>
+      <c r="B165" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="C165" s="26" t="s">
         <v>439</v>
       </c>
-      <c r="B165" s="25" t="s">
+      <c r="D165" s="26" t="s">
         <v>440</v>
-      </c>
-      <c r="C165" s="26" t="s">
-        <v>441</v>
-      </c>
-      <c r="D165" s="26" t="s">
-        <v>442</v>
       </c>
       <c r="E165" s="27">
         <v>40</v>
       </c>
       <c r="F165" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="40" t="s">
+        <v>441</v>
+      </c>
+      <c r="B166" s="25" t="s">
+        <v>442</v>
+      </c>
+      <c r="C166" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="D166" s="26" t="s">
         <v>443</v>
-      </c>
-      <c r="B166" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="C166" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="D166" s="26" t="s">
-        <v>445</v>
       </c>
       <c r="E166" s="27">
         <v>25</v>
       </c>
       <c r="F166" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="40" t="s">
+        <v>444</v>
+      </c>
+      <c r="B167" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="C167" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="D167" s="26" t="s">
         <v>446</v>
-      </c>
-      <c r="B167" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="C167" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="D167" s="26" t="s">
-        <v>448</v>
       </c>
       <c r="E167" s="27">
         <v>18</v>
       </c>
       <c r="F167" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="42" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B168" s="25" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C168" s="30" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D168" s="30" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E168" s="31">
         <v>78</v>
       </c>
       <c r="F168" s="33" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
